--- a/output/roomself_excel/14623.xlsx
+++ b/output/roomself_excel/14623.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>181300</v>
+        <v>61541</v>
       </c>
       <c r="D2" t="n">
-        <v>3440</v>
+        <v>2080</v>
       </c>
       <c r="E2" t="n">
-        <v>672</v>
+        <v>211</v>
       </c>
       <c r="F2" t="n">
-        <v>387</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -488,17 +488,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>61541</v>
+        <v>45732</v>
       </c>
       <c r="D3" t="n">
-        <v>2080</v>
+        <v>1828</v>
       </c>
       <c r="E3" t="n">
-        <v>211</v>
+        <v>148</v>
       </c>
       <c r="F3" t="n">
         <v>22</v>
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>45732</v>
+        <v>181300</v>
       </c>
       <c r="D4" t="n">
-        <v>1828</v>
+        <v>3440</v>
       </c>
       <c r="E4" t="n">
-        <v>148</v>
+        <v>672</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5">
@@ -564,10 +564,10 @@
         <v>2168</v>
       </c>
       <c r="E6" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/14623.xlsx
+++ b/output/roomself_excel/14623.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,23 @@
       <c r="D2" t="n">
         <v>2080</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>211</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>22</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +543,23 @@
       <c r="D3" t="n">
         <v>1828</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>148</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>22</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +576,38 @@
       <c r="D4" t="n">
         <v>3440</v>
       </c>
-      <c r="E4" t="n">
-        <v>672</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>387</v>
+        <v>490</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>369</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>370</v>
+      </c>
+      <c r="M4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +625,38 @@
       <c r="D5" t="n">
         <v>3444</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>371</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>22</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>490</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>345</v>
+      </c>
+      <c r="M5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +674,23 @@
       <c r="D6" t="n">
         <v>2168</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
